--- a/Trans To Vostok/French/Texture.xlsx
+++ b/Trans To Vostok/French/Texture.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SteamLibrary\steamapps\common\Road to Vostok\mods\Trans To Vostok\Trans To Vostok\French\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E48478-3A9C-4794-BDAE-67CDAE0B3276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5E6C86-9A95-498D-BB5B-5AF23D85ADEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,42 +98,10 @@
 and point the character health value</t>
   </si>
   <si>
-    <t>2. Interface
-L'interface est votre interface utilisateur principale, qui contient des éléments
-tels que l'inventaire, l'équipement, les paramètres vitaux et les statistiques
-Vous pouvez accéder à l'interface à l'aide de la touche [TAB]
-Si vous souhaitez obtenir plus d'informations sur un objet, une icône
-ou une valeur spécifique, vous pouvez utiliser l'info-bulle
-Essayez l'info-bulle en ouvrant l'interface
-et en survolant la valeur de santé du personnage</t>
-  </si>
-  <si>
     <t>TX_Tutorial_Interface.png</t>
   </si>
   <si>
     <t>3. Loot &amp; Items</t>
-  </si>
-  <si>
-    <t>3. Loot &amp; Items
-All objects that logically have storage space are 
-interactable loot containers
-Loot is generated to these containers and items 
-are also physically scattered to the game world
-You can open, pick and interact with [MMB]
-When you have items available in Interface, you can 
-choose item actions with Context Menu [RMB]
-Open container and try Context Menu with items</t>
-  </si>
-  <si>
-    <t>3. Butin et objets
-Tous les objets qui disposent logiquement d'un espace de stockage sont 
-des conteneurs de butin avec lesquels on peut interagir
-Le butin est généré dans ces conteneurs et les objets 
-sont également dispersés physiquement dans l'univers du jeu
-Vous pouvez ouvrir, ramasser et interagir avec [bouton central de la souris]
-Lorsque vous avez des objets disponibles dans l'interface, vous pouvez 
-choisir des actions sur les objets via le menu contextuel [bouton droit de la souris]
-Ouvrez un conteneur et essayez le menu contextuel avec les objets</t>
   </si>
   <si>
     <t>TX_Tutorial_Items.png</t>
@@ -153,17 +121,6 @@
 Open container and try equipping items</t>
   </si>
   <si>
-    <t>4. Équipement
-Les emplacements d'équipement sont des emplacements dédiés 
-et sont liés à plusieurs statistiques importantes du personnage
-L'équipement peut augmenter votre capacité de charge [CC] 
-et vous conférer des capacités telles que la lampe torche et la préparation d'un feu
-Vous trouverez les emplacements d'équipement dans l'interface
-Vous pouvez activer les emplacements d'équipement en 
-y plaçant des objets compatibles
-Ouvrez votre sac et essayez d'équiper des objets</t>
-  </si>
-  <si>
     <t>TX_Tutorial_Equipment.png</t>
   </si>
   <si>
@@ -181,79 +138,16 @@
 Open container and try using some medical items</t>
   </si>
   <si>
-    <t>5. Soins et altérations
-Le système de soins repose sur des altérations qui 
-affectent négativement les caractéristiques vitales de votre personnage
-Ces altérations sont représentées par des icônes de soins 
-et vous pouvez les trouver dans l'interface et le HUD
-Lorsqu'une icône de soins devient rouge, l'altération est 
-active et doit être soignée à l'aide d'un objet de soins
-Vous pouvez consulter les causes, les symptômes et les remèdes grâce à l'infobulle
-Ouvrez votre inventaire et essayez d'utiliser quelques objets de soins</t>
-  </si>
-  <si>
     <t>TX_Tutorial_Medical.png</t>
   </si>
   <si>
     <t>6. Weapons</t>
   </si>
   <si>
-    <t>6. Weapons
-Weapons are equipment and they use 
-Primary, Secondary, Knife and Grenade slots
-When a weapon is equipped you can draw 
-and holster from slots with keys [1] [2] [3] [4] [5]
-Every firearm can use Primary slot but only 
-pistols and SMG's can utilize Secondary slot
-Open container, equip a weapon and draw it
-| [RMB] = Aim (ADS) | [F] = Firemode |
-| [MMB] = Canted aim | [X]=Inspect weapon |
-| [SCROLL] = Weapon position | [SCROLL] = Inspect rotation |</t>
-  </si>
-  <si>
-    <t>6. Armes
-Les armes font partie de l'équipement et occupent 
-les emplacements Principal, Secondaire, Couteau et Grenade
-Lorsqu'une arme est équipée, vous pouvez la dégainer 
-et la ranger à l'aide des touches [1] [2] [3] [4] [5]
-Toutes les armes à feu peuvent occuper l'emplacement Principal, mais seuls 
-les pistolets et les mitraillettes peuvent occuper l'emplacement Secondaire
-Ouvrez le conteneur, équipez-vous d'une arme et dégainer
-| [Clic droit] = Viser (ADS) | [F] = Mode de tir |
-| [Clic central] = Viser en inclinaison | [X] = Inspecter l'arme |
-| [MOUSE] = Position de l'arme | [MOUSE] = Inspecter la rotation |</t>
-  </si>
-  <si>
     <t>TX_Tutorial_Weapons.png</t>
   </si>
   <si>
     <t>7. Ammo &amp; Magazines</t>
-  </si>
-  <si>
-    <t>7. Ammo &amp; Magazines
-Weapon system uses seperated magazines
-and caliber-based ammo types
-You can load a magazine by moving a compatible
-ammo type to the magazine with Interface
-You can unload a magazine with Context Menu [RMB]
-Magazines can be attached to weapons manually
-or with [R] which fetches a loaded magazine for you
-Open container, use Tooltip to identify the ammo
-and magazine compatibility, Load -&gt; Attach -&gt; Fire
-[LMB] = Fire [V] = ammo check [CTRL] -&gt; [LMB] = Bullet insert (Bolts &amp; Shotguns)</t>
-  </si>
-  <si>
-    <t>7. Munitions et chargeurs
-Le système d'armes utilise des chargeurs séparés
-et des types de munitions spécifiques à chaque calibre
-Vous pouvez charger un chargeur en déplaçant un type de munition compatible
-vers le chargeur via l'interface
-Vous pouvez décharger un chargeur via le menu contextuel [Clic droit]
-Les chargeurs peuvent être fixés aux armes manuellement
-ou à l'aide de [R], qui va chercher un chargeur chargé pour vous
-Ouvrez le conteneur, utilisez l'info-bulle pour vérifier la compatibilité
-des munitions et du chargeur, puis Chargez -&gt; Fixez -&gt; Tirez
-[Clic gauche] = Tirer [V] = Vérifier les munitions [CTRL] -&gt; [Clic gauche] = Insérer une balle (fusils à verrou et fusils de chasse)</t>
   </si>
   <si>
     <t>TX_Tutorial_Ammo.png</t>
@@ -275,45 +169,10 @@
 [T] = Laser toggle</t>
   </si>
   <si>
-    <t>8. Accessoires
-Vous pouvez personnaliser vos armes en y ajoutant 
-des silencieux, des optiques et des lasers
-Vous pouvez ajouter ou changer d'accessoires, comme les chargeurs, 
-via l'interface, et les retirer à l'aide du menu contextuel
-Ouvrez le conteneur, utilisez l'info-bulle ou les couleurs d'affichage au survol des objets pour 
-vérifier la compatibilité des accessoires et essayez de personnaliser votre arme
-[MAINTENIR CTRL] + [MOUSETTE] = Position du rail optique
-[MOUSETTE] = Niveau de zoom du LPVO
-[ALT] = Optique secondaire
-[T] = Activer/désactiver le laser</t>
-  </si>
-  <si>
     <t>TX_Tutorial_Attachments.png</t>
   </si>
   <si>
     <t>9. Knives &amp; Grenades</t>
-  </si>
-  <si>
-    <t>9. Knives &amp; Grenades
-When a knife is equipped, you can draw it with key [3]
-You can use slash attack with [LMB] 
-and stab attack with [RMB]
-You have two grenades slots and you can draw 
-grenades with keys [4] and [5]
-You can prepare high throw with [LMB] 
-and low throw with [RMB]
-Second press executes and opposite button resets the throw</t>
-  </si>
-  <si>
-    <t>9. Couteaux et grenades
-Lorsqu'un couteau est équipé, vous pouvez le dégainer à l'aide de la touche [3]
-Vous pouvez effectuer une attaque tranchante avec [Clic gauche] 
-et une attaque enfoncée avec [Clic droit]
-Vous disposez de deux emplacements pour les grenades et vous pouvez les dégainer 
-à l'aide des touches [4] et [5]
-Vous pouvez préparer un lancer haut avec [Bouton gauche de la souris] 
-et un lancer bas avec [Bouton droit de la souris]
-Une deuxième pression exécute le lancer et le bouton opposé le réinitialise</t>
   </si>
   <si>
     <t>TX_Tutorial_Grenades.png</t>
@@ -337,6 +196,284 @@
 |NIJ IV = Level 5| 5. Armor plates prevent critical medical condition Rupture|</t>
   </si>
   <si>
+    <t>TX_Tutorial_Armor.png</t>
+  </si>
+  <si>
+    <t>11. Traders</t>
+  </si>
+  <si>
+    <t>TX_Tutorial_Traders.png</t>
+  </si>
+  <si>
+    <t>12. AI</t>
+  </si>
+  <si>
+    <t>12. AI
+AI is divided into three hostile factions which
+ocupy different areas of the game world
+|Area05|Border Zone| Vostok|
+|Bandits|Guards|Military|
+|Easy AI|Medium AI|Hard AI|
+Each AI faction has different abilities and
+faction bosses with rare spawn changes
+Map instances can spawn maximum of 10 AI's
+once you have eliminated all, you will have peace</t>
+  </si>
+  <si>
+    <t>TX_Tutorial_AI.png</t>
+  </si>
+  <si>
+    <t>13. Maps &amp; Transitions</t>
+  </si>
+  <si>
+    <t>13. Maps &amp; Transitions
+Like AI, game world is divided into three zones which have different maps and loot pools
+|Starting zone | Divider zone | Permadeath zone |
+|Area 05 | Border Zone | Vostok |
+|Low-tier loot | Medium-tier loot | High-tier loot|
+You can travel through these zones and maps 
+through Transitions which have certain travel costs 
+related to character vitals and World Simulation
+Transitions are marked with Transition Flags</t>
+  </si>
+  <si>
+    <t>TX_Tutorial_Maps.png</t>
+  </si>
+  <si>
+    <t>14. World Simulation</t>
+  </si>
+  <si>
+    <t>14. World Simulation
+Game uses World Simulation which creates 
+day &amp; night cycles, dynamic weather, 
+seasons and randomized events
+Simulation rate
+Day &amp; night cycle (24h) = 2.4h IRL
+World Simulation is linked to sleeping and 
+map transitions which increases simulation time
+You can see current time with time related items 
+Pick a time item (Alarm Clock) and equip it
+*Simulation time stays locked during Tutorial</t>
+  </si>
+  <si>
+    <t>TX_Tutorial_World.png</t>
+  </si>
+  <si>
+    <t>15. Shelters</t>
+  </si>
+  <si>
+    <t>15. Shelters
+Shelters are safe areas that allows you to save 
+simulation time, character progress and loot
+Shelters can be unlocked with keys 
+which you acquire by completing tasks
+All Shelters can be customized with 
+Item Placement and Decor Mode
+You can use Item Placement with [G] and move 
+furniture by activating Decor Mode with [F1]</t>
+  </si>
+  <si>
+    <t>TX_Tutorial_Shelters.png</t>
+  </si>
+  <si>
+    <t>16. Vostok</t>
+  </si>
+  <si>
+    <t>16. Vostok
+Vostok is a high-risk, high-reward Permadeath zone 
+where death results losing all existing progression
+Permadeath in this game deletes all save files, 
+so you lose absolutely everything
+When you travel towards Vostok maps,
+ you are warned before the Transition
+When you enter Vostok maps a red 
+Permadeath Skull will also appear 
+in the upper corner of the screen</t>
+  </si>
+  <si>
+    <t>TX_Tutorial_Vostok.png</t>
+  </si>
+  <si>
+    <t>Permadeath Skull Icon: https://pixabay.com/ko/photos/%eb%91%90%ea%b0%9c%ea%b3%a8-%ea%b3%b5%ed%8f%ac-%ed%95%b4%ea%b3%a8-8964071/</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>Worldmap</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>UI\Sprites</t>
+  </si>
+  <si>
+    <t>World_Map.png</t>
+  </si>
+  <si>
+    <t>Aerial Image: Copernicus Sentinel data 2026, processed with Corpernicus Browser
+Crumpled Paper: Pixabay (https://pixabay.com/ko/photos/%ea%b5%ac%ea%b2%a8%ec%a7%84-%ec%a2%85%ec%9d%b4-%eb%b8%94%eb%9e%99-%ec%a2%85%ec%9d%b4-6793287/)
+Airplane Icon: Pixabay (https://pixabay.com/vectors/airplane-)transportation-symbol-icon-23997/
+Masking Tape: Texturelabs (https://texturelabs.org/textures/details_122/)</t>
+  </si>
+  <si>
+    <t>1. Paramètres
+Bienvenue dans le tutoriel de Road to Vostok
+Ce tutoriel vous guidera à travers les
+mécaniques de jeu et les commandes les plus importantes
+Commençons par les paramètres
+Vous pouvez accéder aux paramètres à l'aide de la touche [ESC]
+Ces paramètres vous permettent de modifier les commandes,
+diverses valeurs système et les options de performances
+?? = Options de performances</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. Interface
+L'interface est votre interface utilisateur principale, qui contient des éléments
+tels que l'inventaire, l'équipement, les paramètres vitaux et les statistiques
+Vous pouvez accéder à l'interface à l'aide de la touche [TAB]
+Si vous souhaitez obtenir plus d'informations sur un objet, une icône
+ou une valeur spécifique, vous pouvez utiliser l'info-bulle
+Essayez l'info-bulle en ouvrant l'interface
+et en survolant la valeur de santé du personnage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Butin et objets
+Tous les objets qui disposent logiquement d'un espace de stockage sont 
+des conteneurs de butin avec lesquels on peut interagir
+Le butin est généré dans ces conteneurs et les objets 
+sont également dispersés physiquement dans l'univers du jeu
+Vous pouvez ouvrir, ramasser et interagir avec [bouton central de la souris]
+Lorsque vous avez des objets disponibles dans l'interface, vous pouvez 
+choisir des actions sur les objets via le menu contextuel [bouton droit de la souris]
+Ouvrez un conteneur et essayez le menu contextuel avec les objets</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Loot &amp; Items
+All objects that logically have storage space are 
+interactable loot containers
+Loot is generated to these containers and items 
+are also physically scattered to the game world
+You can open, pick and interact with [MMB]
+When you have items available in Interface, you can 
+choose item actions with Context Menu [RMB]
+Open container and try Context Menu with items</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. Soins et altérations
+Le système de soins repose sur des altérations qui 
+affectent négativement les caractéristiques vitales de votre personnage
+Ces altérations sont représentées par des icônes de soins 
+et vous pouvez les trouver dans l'interface et le HUD
+Lorsqu'une icône de soins devient rouge, l'altération est 
+active et doit être soignée à l'aide d'un objet de soins
+Vous pouvez consulter les causes, les symptômes et les remèdes grâce à l'infobulle
+Ouvrez votre inventaire et essayez d'utiliser quelques objets de soins</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. Équipement
+Les emplacements d'équipement sont des emplacements dédiés 
+et sont liés à plusieurs statistiques importantes du personnage
+L'équipement peut augmenter votre capacité de charge [CC] 
+et vous conférer des capacités telles que la lampe torche et la préparation d'un feu
+Vous trouverez les emplacements d'équipement dans l'interface
+Vous pouvez activer les emplacements d'équipement en 
+y plaçant des objets compatibles
+Ouvrez votre sac et essayez d'équiper des objets</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. Weapons
+Weapons are equipment and they use 
+Primary, Secondary, Knife and Grenade slots
+When a weapon is equipped you can draw 
+and holster from slots with keys [1] [2] [3] [4] [5]
+Every firearm can use Primary slot but only 
+pistols and SMG's can utilize Secondary slot
+Open container, equip a weapon and draw it
+| [RMB] = Aim (ADS) | [F] = Firemode |
+| [MMB] = Canted aim | [X]=Inspect weapon |
+| [SCROLL] = Weapon position | [SCROLL] = Inspect rotation |</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. Armes
+Les armes font partie de l'équipement et occupent 
+les emplacements Principal, Secondaire, Couteau et Grenade
+Lorsqu'une arme est équipée, vous pouvez la dégainer 
+et la ranger à l'aide des touches [1] [2] [3] [4] [5]
+Toutes les armes à feu peuvent occuper l'emplacement Principal, mais seuls 
+les pistolets et les mitraillettes peuvent occuper l'emplacement Secondaire
+Ouvrez le conteneur, équipez-vous d'une arme et dégainer
+| [Clic droit] = Viser (ADS) | [F] = Mode de tir |
+| [Clic central] = Viser en inclinaison | [X] = Inspecter l'arme |
+| [SCROLL] = Position de l'arme | [SCROLL] = Inspecter la rotation |</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7. Munitions et chargeurs
+Le système d'armes utilise des chargeurs séparés
+et des types de munitions spécifiques à chaque calibre
+Vous pouvez charger un chargeur en déplaçant un type de munition compatible
+vers le chargeur via l'interface
+Vous pouvez décharger un chargeur via le menu contextuel [Clic droit]
+Les chargeurs peuvent être fixés aux armes manuellement
+ou à l'aide de [R], qui va chercher un chargeur chargé pour vous
+Ouvrez le conteneur, utilisez l'info-bulle pour vérifier la compatibilité
+des munitions et du chargeur, puis Chargez -&gt; Fixez -&gt; Tirez
+[Clic gauche] = Tirer [V] = Vérifier les munitions [CTRL] -&gt; [Clic gauche] = Insérer une balle (fusils à verrou et fusils de chasse)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7. Ammo &amp; Magazines
+Weapon system uses seperated magazines
+and caliber-based ammo types
+You can load a magazine by moving a compatible
+ammo type to the magazine with Interface
+You can unload a magazine with Context Menu [RMB]
+Magazines can be attached to weapons manually
+or with [R] which fetches a loaded magazine for you
+Open container, use Tooltip to identify the ammo
+and magazine compatibility, Load -&gt; Attach -&gt; Fire
+[LMB] = Fire [V] = ammo check [CTRL] -&gt; [LMB] = Bullet insert (Bolts &amp; Shotguns)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8. Accessoires
+Vous pouvez personnaliser vos armes en y ajoutant 
+des silencieux, des optiques et des lasers
+Vous pouvez ajouter ou changer d'accessoires, comme les chargeurs, 
+via l'interface, et les retirer à l'aide du menu contextuel
+Ouvrez le conteneur, utilisez l'info-bulle ou les couleurs d'affichage au survol des objets pour 
+vérifier la compatibilité des accessoires et essayez de personnaliser votre arme
+[MAINTENIR CTRL] + [MOUSETTE] = Position du rail optique
+[MOUSETTE] = Niveau de zoom du LPVO
+[ALT] = Optique secondaire
+[T] = Activer/désactiver le laser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9. Knives &amp; Grenades
+When a knife is equipped, you can draw it with key [3]
+You can use slash attack with [LMB] 
+and stab attack with [RMB]
+You have two grenades slots and you can draw 
+grenades with keys [4] and [5]
+You can prepare high throw with [LMB] 
+and low throw with [RMB]
+Second press executes and opposite button resets the throw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>10. Armure
 Le système d'armure repose sur des casques, des plaques de protection et des gilets pare-balles (rigs) certifiés NIJ (niveaux II à IV)
 Le niveau de protection de l'armure est directement lié
@@ -349,12 +486,32 @@
 |NIJ III = Niveau 3| 3. Une pénétration de niveau supérieur brise l'armure immédiatement|
 |NIJ III+ = Niveau 4| 4. Les casques préviennent l'état médical critique « Coup à la tête »|
 |NIJ IV = Niveau 5| 5. Les plaques de blindage préviennent l'état médical critique « Rupture »|</t>
-  </si>
-  <si>
-    <t>TX_Tutorial_Armor.png</t>
-  </si>
-  <si>
-    <t>11. Traders</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9. Couteaux &amp; Grenades
+Lorsqu'un couteau est équipé, vous pouvez le dégainer à l'aide de la touche [3]
+Vous pouvez effectuer une attaque tranchante avec [Clic gauche] 
+et une attaque enfoncée avec [Clic droit]
+Vous disposez de deux emplacements pour les grenades et vous pouvez les dégainer 
+à l'aide des touches [4] et [5]
+Vous pouvez préparer un lancer haut avec [Bouton gauche de la souris] 
+et un lancer bas avec [Bouton droit de la souris]
+Une deuxième pression exécute le lancer et le bouton opposé le réinitialise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11. Les marchands
+Les marchands sont des personnages du jeu qui vous permettent 
+d'échanger des objets et d'accomplir des quêtes liées à l'univers du jeu
+Le système d'échange repose sur le troc, votre objectif 
+étant de conclure un accord aussi équilibré que possible.
+La transaction est calculée en fonction de la valeur des objets demandés, de la taxe du marchand et de la valeur des objets proposés.
+Accomplir des quêtes réduira la taxe du marchand et vous permettra d'obtenir 
+des objets de récompense ainsi que des clés pour débloquer de nouveaux abris.
+Interagissez avec le marchand généraliste et essayez d'
+échanger quelque chose et d'accomplir une quête.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>11. Traders
@@ -367,36 +524,7 @@
 you reward items and keys for unlocking new Shelters
 Interact with trader Generalist and try 
 trading something and completing a task</t>
-  </si>
-  <si>
-    <t>11. Les marchands
-Les marchands sont des personnages du jeu qui vous permettent 
-d'échanger des objets et d'accomplir des quêtes liées à l'univers du jeu
-Le système d'échange repose sur le troc, votre objectif 
-étant de conclure un accord aussi équilibré que possible.
-La transaction est calculée en fonction de la valeur des objets demandés, de la taxe du marchand et de la valeur des objets proposés.
-Accomplir des quêtes réduira la taxe du marchand et vous permettra d'obtenir 
-des objets de récompense ainsi que des clés pour débloquer de nouveaux abris.
-Interagissez avec le marchand généraliste et essayez d'
-échanger quelque chose et d'accomplir une quête.</t>
-  </si>
-  <si>
-    <t>TX_Tutorial_Traders.png</t>
-  </si>
-  <si>
-    <t>12. AI</t>
-  </si>
-  <si>
-    <t>12. AI
-AI is divided into three hostile factions which
-ocupy different areas of the game world
-|Area05|Border Zone| Vostok|
-|Bandits|Guards|Military|
-|Easy AI|Medium AI|Hard AI|
-Each AI faction has different abilities and
-faction bosses with rare spawn changes
-Map instances can spawn maximum of 10 AI's
-once you have eliminated all, you will have peace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>12. IA
@@ -409,26 +537,10 @@
 des chefs de faction dont l'apparition varie
 Les instances de carte peuvent générer jusqu'à 10 IA
 une fois que vous les aurez toutes éliminées, vous aurez la paix</t>
-  </si>
-  <si>
-    <t>TX_Tutorial_AI.png</t>
-  </si>
-  <si>
-    <t>13. Maps &amp; Transitions</t>
-  </si>
-  <si>
-    <t>13. Maps &amp; Transitions
-Like AI, game world is divided into three zones which have different maps and loot pools
-|Starting zone | Divider zone | Permadeath zone |
-|Area 05 | Border Zone | Vostok |
-|Low-tier loot | Medium-tier loot | High-tier loot|
-You can travel through these zones and maps 
-through Transitions which have certain travel costs 
-related to character vitals and World Simulation
-Transitions are marked with Transition Flags</t>
-  </si>
-  <si>
-    <t>13. Cartes et transitions
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13. Cartes &amp; transitions
 Tout comme l'IA, l'univers du jeu est divisé en trois zones qui comportent des cartes et des pools de butin différents
 |Zone de départ | Zone de transition | Zone de mort permanente |
 |Zone 05 | Zone frontalière | Vostok |
@@ -437,124 +549,7 @@
 grâce à des transitions qui impliquent certains coûts de déplacement 
 liés aux caractéristiques du personnage et à la simulation du monde.
 Les transitions sont signalées par des drapeaux de transition.</t>
-  </si>
-  <si>
-    <t>TX_Tutorial_Maps.png</t>
-  </si>
-  <si>
-    <t>14. World Simulation</t>
-  </si>
-  <si>
-    <t>14. World Simulation
-Game uses World Simulation which creates 
-day &amp; night cycles, dynamic weather, 
-seasons and randomized events
-Simulation rate
-Day &amp; night cycle (24h) = 2.4h IRL
-World Simulation is linked to sleeping and 
-map transitions which increases simulation time
-You can see current time with time related items 
-Pick a time item (Alarm Clock) and equip it
-*Simulation time stays locked during Tutorial</t>
-  </si>
-  <si>
-    <t>TX_Tutorial_World.png</t>
-  </si>
-  <si>
-    <t>15. Shelters</t>
-  </si>
-  <si>
-    <t>15. Shelters
-Shelters are safe areas that allows you to save 
-simulation time, character progress and loot
-Shelters can be unlocked with keys 
-which you acquire by completing tasks
-All Shelters can be customized with 
-Item Placement and Decor Mode
-You can use Item Placement with [G] and move 
-furniture by activating Decor Mode with [F1]</t>
-  </si>
-  <si>
-    <t>15. Abris
-Les abris sont des zones sécurisées qui vous permettent de sauvegarder 
-votre progression dans la simulation, celle de votre personnage et votre butin
-Les abris peuvent être déverrouillés à l'aide de clés 
-que vous obtenez en accomplissant des tâches
-Tous les abris peuvent être personnalisés grâce au 
-mode « Placement d'objets » et au mode « Décoration »
-Vous pouvez utiliser le mode « Placement d'objets » avec la touche [G] et déplacer 
-les meubles en activant le mode « Décoration » avec la touche [F1]</t>
-  </si>
-  <si>
-    <t>TX_Tutorial_Shelters.png</t>
-  </si>
-  <si>
-    <t>16. Vostok</t>
-  </si>
-  <si>
-    <t>16. Vostok
-Vostok is a high-risk, high-reward Permadeath zone 
-where death results losing all existing progression
-Permadeath in this game deletes all save files, 
-so you lose absolutely everything
-When you travel towards Vostok maps,
- you are warned before the Transition
-When you enter Vostok maps a red 
-Permadeath Skull will also appear 
-in the upper corner of the screen</t>
-  </si>
-  <si>
-    <t>16. Vostok
-Vostok est une zone Permadeath à haut risque et à haut rendement 
-où la mort entraîne la perte de toute progression
-Dans ce jeu, le Permadeath supprime tous les fichiers de sauvegarde, 
-vous perdez donc absolument tout
-Lorsque vous vous dirigez vers les cartes de Vostok,
- vous recevez un avertissement avant la transition
-Lorsque vous entrez dans les cartes de Vostok, un 
-crâne Permadeath rouge apparaît également 
-dans le coin supérieur de l'écran</t>
-  </si>
-  <si>
-    <t>TX_Tutorial_Vostok.png</t>
-  </si>
-  <si>
-    <t>Permadeath Skull Icon: https://pixabay.com/ko/photos/%eb%91%90%ea%b0%9c%ea%b3%a8-%ea%b3%b5%ed%8f%ac-%ed%95%b4%ea%b3%a8-8964071/</t>
-  </si>
-  <si>
-    <t>UI</t>
-  </si>
-  <si>
-    <t>Map</t>
-  </si>
-  <si>
-    <t>Worldmap</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>UI\Sprites</t>
-  </si>
-  <si>
-    <t>World_Map.png</t>
-  </si>
-  <si>
-    <t>Aerial Image: Copernicus Sentinel data 2026, processed with Corpernicus Browser
-Crumpled Paper: Pixabay (https://pixabay.com/ko/photos/%ea%b5%ac%ea%b2%a8%ec%a7%84-%ec%a2%85%ec%9d%b4-%eb%b8%94%eb%9e%99-%ec%a2%85%ec%9d%b4-6793287/)
-Airplane Icon: Pixabay (https://pixabay.com/vectors/airplane-)transportation-symbol-icon-23997/
-Masking Tape: Texturelabs (https://texturelabs.org/textures/details_122/)</t>
-  </si>
-  <si>
-    <t>1. Paramètres
-Bienvenue dans le tutoriel de Road to Vostok
-Ce tutoriel vous guidera à travers les
-mécaniques de jeu et les commandes les plus importantes
-Commençons par les paramètres
-Vous pouvez accéder aux paramètres à l'aide de la touche [ESC]
-Ces paramètres vous permettent de modifier les commandes,
-diverses valeurs système et les options de performances
-?? = Options de performances</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>14. Simulation du monde
@@ -568,6 +563,32 @@
 Vous pouvez voir l'heure actuelle grâce aux objets liés au temps
 Choisissez un objet lié au temps (réveil) et équipez-le
 *Le temps de simulation reste verrouillé pendant le tutoriel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15. Abris
+Les abris sont des zones sécurisées qui vous permettent de sauvegarder 
+votre progression dans la simulation, celle de votre personnage et votre butin
+Les abris peuvent être déverrouillés à l'aide de clés 
+que vous obtenez en accomplissant des tâches
+Tous les abris peuvent être personnalisés grâce au 
+mode « Placement d'objets » et au mode « Décoration »
+Vous pouvez utiliser le mode « Placement d'objets » avec la touche [G] et déplacer 
+les meubles en activant le mode « Décoration » avec la touche [F1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16. Vostok
+Vostok est une zone Permadeath à haut risque et à haut rendement 
+où la mort entraîne la perte de toute progression
+Dans ce jeu, le Permadeath supprime tous les fichiers de sauvegarde, 
+vous perdez donc absolument tout
+Lorsque vous vous dirigez vers les cartes de Vostok,
+ vous recevez un avertissement avant la transition
+Lorsque vous entrez dans les cartes de Vostok, un 
+crâne Permadeath rouge apparaît également 
+dans le coin supérieur de l'écran</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1083,7 +1104,7 @@
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>14</v>
@@ -1112,13 +1133,13 @@
         <v>19</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>16</v>
@@ -1132,19 +1153,19 @@
         <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>16</v>
@@ -1158,19 +1179,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>16</v>
@@ -1184,19 +1205,19 @@
         <v>11</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>16</v>
@@ -1210,19 +1231,19 @@
         <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>16</v>
@@ -1236,19 +1257,19 @@
         <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>16</v>
@@ -1262,19 +1283,19 @@
         <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>16</v>
@@ -1288,19 +1309,19 @@
         <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>16</v>
@@ -1314,19 +1335,19 @@
         <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>16</v>
@@ -1340,19 +1361,19 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>16</v>
@@ -1366,19 +1387,19 @@
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>16</v>
@@ -1392,19 +1413,19 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>16</v>
@@ -1418,19 +1439,19 @@
         <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>16</v>
@@ -1444,19 +1465,19 @@
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>16</v>
@@ -1470,25 +1491,25 @@
         <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1546,31 +1567,31 @@
     </row>
     <row r="2" spans="1:10" ht="174" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:10">
